--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487186_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487186_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8484</v>
+        <v>5.0467</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6318</v>
+        <v>3.1513</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2166</v>
+        <v>1.8954</v>
       </c>
       <c r="G2" t="n">
         <v>2.6307</v>
@@ -610,13 +610,13 @@
         <v>2.7021</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1295</v>
+        <v>0.3278</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8328</v>
+        <v>-0.3133</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9624</v>
+        <v>0.6411</v>
       </c>
       <c r="V2" t="n">
         <v>-0.614</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6881</v>
+        <v>3.4927</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3175</v>
+        <v>0.0762</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3706</v>
+        <v>3.4165</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7603</v>
+        <v>2.2895</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.29</v>
+        <v>0.7058</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0503</v>
+        <v>1.5837</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3272</v>
+        <v>2.836</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0159</v>
+        <v>0.419</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3431</v>
+        <v>2.417</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5669</v>
+        <v>-0.5464</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2741</v>
+        <v>0.2868</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2928</v>
+        <v>-0.8333</v>
       </c>
       <c r="P3" t="n">
-        <v>0.193</v>
+        <v>-0.772</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.8951</v>
+        <v>-3.8602</v>
       </c>
       <c r="R3" t="n">
         <v>3.0881</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4067</v>
+        <v>0.7472</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5996</v>
+        <v>-0.4134</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8070000000000001</v>
+        <v>1.1607</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3281</v>
+        <v>1.228</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0422</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4421</v>
+        <v>2.9652</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4027</v>
+        <v>2.5278</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8448</v>
+        <v>0.4374</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2895</v>
+        <v>1.9995</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7058</v>
+        <v>1.7046</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5837</v>
+        <v>0.2949</v>
       </c>
       <c r="J4" t="n">
-        <v>2.836</v>
+        <v>2.3797</v>
       </c>
       <c r="K4" t="n">
-        <v>0.419</v>
+        <v>2.339</v>
       </c>
       <c r="L4" t="n">
-        <v>2.417</v>
+        <v>0.0407</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5464</v>
+        <v>-0.3802</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2868</v>
+        <v>-0.6344</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8333</v>
+        <v>0.2542</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.772</v>
+        <v>0.772</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0881</v>
+        <v>0.772</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6967</v>
+        <v>0.1937</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8923</v>
+        <v>0.1481</v>
       </c>
       <c r="U4" t="n">
-        <v>1.589</v>
+        <v>0.0456</v>
       </c>
       <c r="V4" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3122</v>
+        <v>2.4914</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9283</v>
+        <v>-0.906</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3839</v>
+        <v>3.3973</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9995</v>
+        <v>0.7603</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7046</v>
+        <v>-0.29</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2949</v>
+        <v>1.0503</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3797</v>
+        <v>1.3272</v>
       </c>
       <c r="K5" t="n">
-        <v>2.339</v>
+        <v>-0.0159</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0407</v>
+        <v>1.3431</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3802</v>
+        <v>-0.5669</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6344</v>
+        <v>-0.2741</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2542</v>
+        <v>-0.2928</v>
       </c>
       <c r="P5" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R5" t="n">
-        <v>0.772</v>
+        <v>3.0881</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5407</v>
+        <v>1.2099</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5486</v>
+        <v>0.3761</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.8338</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3281</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6691</v>
+        <v>2.0498</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2904</v>
+        <v>0.3499</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3787</v>
+        <v>1.6999</v>
       </c>
       <c r="G6" t="n">
         <v>2.2469</v>
@@ -922,13 +922,13 @@
         <v>2.3161</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2617</v>
+        <v>0.119</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1652</v>
+        <v>-0.1057</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0965</v>
+        <v>0.2247</v>
       </c>
       <c r="V6" t="n">
         <v>1.228</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. OLIVEIRA GETE</t>
+          <t>M. ZUBIZARRETA ALBIZU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2446</v>
+        <v>0.1014</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0537</v>
+        <v>-1.4084</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8091</v>
+        <v>1.5098</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9999</v>
+        <v>1.0287</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6393</v>
+        <v>0.8559</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6394</v>
+        <v>0.1728</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7469</v>
+        <v>1.7623</v>
       </c>
       <c r="K7" t="n">
-        <v>2.96</v>
+        <v>1.0297</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2131</v>
+        <v>0.7326</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.747</v>
+        <v>-0.7336</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3207</v>
+        <v>-0.1738</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4263</v>
+        <v>-0.5598</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.965</v>
+        <v>-1.158</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.8602</v>
+        <v>-2.8951</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8951</v>
+        <v>1.7371</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3768</v>
+        <v>0.2307</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2842</v>
+        <v>-0.2756</v>
       </c>
       <c r="U7" t="n">
-        <v>0.661</v>
+        <v>0.5063</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ZUBIZARRETA ALBIZU</t>
+          <t>A. OLIVEIRA GETE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.325</v>
+        <v>-0.2129</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7277</v>
+        <v>-3.0755</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4027</v>
+        <v>2.8626</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0287</v>
+        <v>0.9999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8559</v>
+        <v>2.6393</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1728</v>
+        <v>-1.6394</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7623</v>
+        <v>1.7469</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0297</v>
+        <v>2.96</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7326</v>
+        <v>-1.2131</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7336</v>
+        <v>-0.747</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1738</v>
+        <v>-0.3207</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5598</v>
+        <v>-0.4263</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.158</v>
+        <v>-0.965</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.8951</v>
+        <v>-3.8602</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7371</v>
+        <v>2.8951</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1957</v>
+        <v>0.4085</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5949</v>
+        <v>-0.306</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3992</v>
+        <v>0.7145</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>E. JUARROS CASTAÑO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5733</v>
+        <v>-0.3787</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0407</v>
+        <v>-1.4537</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.614</v>
+        <v>1.075</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5733</v>
+        <v>-1.2947</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.207</v>
+        <v>-0.5557</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3663</v>
+        <v>-0.739</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0407</v>
+        <v>-0.4206</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.1656</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0407</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.614</v>
+        <v>-0.8741</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.207</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.407</v>
+        <v>-0.1528</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0.2191</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.3539</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.1348</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. LARRAÑAGA ORMAZABAL</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9258</v>
+        <v>-0.5733</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0376</v>
+        <v>0.0407</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9634</v>
+        <v>-0.614</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0149</v>
+        <v>-0.5733</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3985</v>
+        <v>-0.207</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4134</v>
+        <v>-0.3663</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1332</v>
+        <v>0.0407</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8008</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6676</v>
+        <v>0.0407</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1481</v>
+        <v>-0.614</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4023</v>
+        <v>-0.207</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2542</v>
+        <v>-0.407</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.386</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5248</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4164</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1084</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. JUARROS CASTAÑO</t>
+          <t>M. LARRAÑAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0599</v>
+        <v>-0.5787</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8136</v>
+        <v>0.4382</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7538</v>
+        <v>-1.0169</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2947</v>
+        <v>-0.0149</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5557</v>
+        <v>0.3985</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.739</v>
+        <v>-0.4134</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4206</v>
+        <v>1.1332</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1656</v>
+        <v>1.8008</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.6676</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8741</v>
+        <v>-1.1481</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-1.4023</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1528</v>
+        <v>0.2542</v>
       </c>
       <c r="P11" t="n">
-        <v>0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.965</v>
       </c>
       <c r="R11" t="n">
-        <v>1.158</v>
+        <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9003</v>
+        <v>-0.1778</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7139</v>
+        <v>-0.0159</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1864</v>
+        <v>-0.162</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0.2859</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6562</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7241</v>
+        <v>-2.4039</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4183</v>
+        <v>-2.0177</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3058</v>
+        <v>-0.3861</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9244</v>
@@ -1390,13 +1390,13 @@
         <v>0.965</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1858</v>
+        <v>0.1345</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4164</v>
+        <v>-0.0159</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2307</v>
+        <v>0.1504</v>
       </c>
       <c r="V12" t="n">
         <v>-0.614</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.1072</v>
+        <v>11.9997</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.169700000000001</v>
+        <v>-2.277200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>14.277</v>
+        <v>14.2769</v>
       </c>
       <c r="G13" t="n">
         <v>8.148199999999999</v>
@@ -1438,7 +1438,7 @@
         <v>8.880099999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7317999999999999</v>
+        <v>-0.7317999999999998</v>
       </c>
       <c r="J13" t="n">
         <v>16.3209</v>
@@ -1459,7 +1459,7 @@
         <v>-1.5603</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9649999999999999</v>
+        <v>-0.9649999999999997</v>
       </c>
       <c r="Q13" t="n">
         <v>-20.2658</v>
@@ -1468,13 +1468,13 @@
         <v>19.3006</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0821</v>
+        <v>2.9744</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.1679</v>
+        <v>-1.2755</v>
       </c>
       <c r="U13" t="n">
-        <v>4.250100000000001</v>
+        <v>4.2499</v>
       </c>
       <c r="V13" t="n">
         <v>1.842</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. VICUÑA ROYO</t>
+          <t>M. BIDAURRE SOLA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.848</v>
+        <v>1.4789</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9370000000000001</v>
+        <v>-0.6301</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9111</v>
+        <v>2.109</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6569</v>
+        <v>0.3212</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8996</v>
+        <v>-1.0805</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5566</v>
+        <v>1.4016</v>
       </c>
       <c r="J14" t="n">
-        <v>1.478</v>
+        <v>2.1632</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1756</v>
+        <v>0.2018</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3024</v>
+        <v>1.9614</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.821</v>
+        <v>-1.842</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0752</v>
+        <v>-1.2822</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2542</v>
+        <v>-0.5598</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.579</v>
+        <v>0.965</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.5091</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9301</v>
+        <v>3.4741</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1984</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1105</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.4769</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5717</v>
+        <v>0.2859</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8576</v>
+        <v>0.2859</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. BIDAURRE SOLA</t>
+          <t>I. VICUÑA ROYO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7373</v>
+        <v>0.7197</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1308</v>
+        <v>-0.1646</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8681</v>
+        <v>0.8843</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3212</v>
+        <v>0.6569</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0805</v>
+        <v>-0.8996</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4016</v>
+        <v>1.5566</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1632</v>
+        <v>1.478</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2018</v>
+        <v>0.1756</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9614</v>
+        <v>1.3024</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.842</v>
+        <v>-0.821</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2822</v>
+        <v>-1.0752</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5598</v>
+        <v>0.2542</v>
       </c>
       <c r="P15" t="n">
-        <v>0.965</v>
+        <v>-0.579</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.5091</v>
       </c>
       <c r="R15" t="n">
-        <v>3.4741</v>
+        <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8348</v>
+        <v>0.0701</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0708</v>
+        <v>0.0089</v>
       </c>
       <c r="U15" t="n">
-        <v>0.236</v>
+        <v>0.0611</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2859</v>
+        <v>0.5717</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2859</v>
+        <v>0.8576</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6254</v>
+        <v>-0.2828</v>
       </c>
       <c r="E16" t="n">
-        <v>1.307</v>
+        <v>0.5059</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6816</v>
+        <v>-0.7887</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6484</v>
@@ -1702,13 +1702,13 @@
         <v>1.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3088</v>
+        <v>0.4006</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1105</v>
+        <v>0.3094</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1983</v>
+        <v>0.0912</v>
       </c>
       <c r="V16" t="n">
         <v>-0.614</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6745</v>
+        <v>-0.5545</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2347</v>
+        <v>0.435</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9092</v>
+        <v>-0.9896</v>
       </c>
       <c r="G17" t="n">
         <v>2.0321</v>
@@ -1780,13 +1780,13 @@
         <v>1.7371</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8996</v>
+        <v>-0.7796</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1303</v>
+        <v>-0.93</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2307</v>
+        <v>0.1504</v>
       </c>
       <c r="V17" t="n">
         <v>-1.228</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9944</v>
+        <v>-0.8011</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9424</v>
+        <v>-0.6419</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.052</v>
+        <v>-0.1591</v>
       </c>
       <c r="G18" t="n">
         <v>0.0931</v>
@@ -1858,13 +1858,13 @@
         <v>2.1231</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3384</v>
+        <v>-0.1451</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8923</v>
+        <v>-0.5919</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.4468</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9421</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7503</v>
+        <v>-1.1762</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9771</v>
+        <v>-1.3762</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2268</v>
+        <v>0.2</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7763</v>
@@ -1936,13 +1936,13 @@
         <v>1.7371</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9234</v>
+        <v>-0.3493</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9518</v>
+        <v>-0.351</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0284</v>
+        <v>0.0016</v>
       </c>
       <c r="V19" t="n">
         <v>0.3704</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. OREJA ELSO</t>
+          <t>J. ZHANG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9697</v>
+        <v>-1.9371</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6482</v>
+        <v>-3.8286</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3214</v>
+        <v>1.8915</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0241</v>
+        <v>-2.0224</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0991</v>
+        <v>-0.0703</v>
       </c>
       <c r="I20" t="n">
-        <v>0.075</v>
+        <v>-1.9521</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1642</v>
+        <v>-0.6609</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0828</v>
+        <v>1.1385</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0814</v>
+        <v>-1.7993</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1883</v>
+        <v>-1.3616</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1819</v>
+        <v>-1.2087</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0064</v>
+        <v>-0.1528</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.158</v>
+        <v>0.579</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1231</v>
+        <v>-2.3161</v>
       </c>
       <c r="R20" t="n">
-        <v>0.965</v>
+        <v>2.8951</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4984</v>
+        <v>-0.4938</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3107</v>
+        <v>-0.8517</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1877</v>
+        <v>0.3579</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ZHANG</t>
+          <t>H. OREJA ELSO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2782</v>
+        <v>-2.0232</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.9288</v>
+        <v>-1.6482</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6505</v>
+        <v>-0.375</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0224</v>
+        <v>-1.0241</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0703</v>
+        <v>-1.0991</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9521</v>
+        <v>0.075</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6609</v>
+        <v>0.1642</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1385</v>
+        <v>0.0828</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7993</v>
+        <v>0.0814</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3616</v>
+        <v>-1.1883</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2087</v>
+        <v>-1.1819</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1528</v>
+        <v>-0.0064</v>
       </c>
       <c r="P21" t="n">
-        <v>0.579</v>
+        <v>-1.158</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3161</v>
+        <v>-2.1231</v>
       </c>
       <c r="R21" t="n">
-        <v>2.8951</v>
+        <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8348</v>
+        <v>0.4449</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9518</v>
+        <v>0.3107</v>
       </c>
       <c r="U21" t="n">
-        <v>0.117</v>
+        <v>0.1342</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1739</v>
+        <v>-2.7594</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3505</v>
+        <v>-2.1502</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8233</v>
+        <v>-0.6092</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3357</v>
@@ -2170,13 +2170,13 @@
         <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2241</v>
+        <v>-0.8097</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8923</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3318</v>
+        <v>-0.1177</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4771</v>
+        <v>-3.7715</v>
       </c>
       <c r="E23" t="n">
         <v>-4.7779</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3008</v>
+        <v>1.0063</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4447</v>
@@ -2248,13 +2248,13 @@
         <v>2.1231</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0324</v>
+        <v>-0.3269</v>
       </c>
       <c r="T23" t="n">
         <v>-0.8923</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8599</v>
+        <v>0.5655</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-11.1074</v>
+        <v>-11.1072</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.277</v>
+        <v>-14.2768</v>
       </c>
       <c r="F24" t="n">
-        <v>3.1698</v>
+        <v>3.1695</v>
       </c>
       <c r="G24" t="n">
         <v>-8.148300000000001</v>
@@ -2326,13 +2326,13 @@
         <v>20.2659</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.0819</v>
+        <v>-2.082</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.2499</v>
+        <v>-4.25</v>
       </c>
       <c r="U24" t="n">
-        <v>2.168</v>
+        <v>2.1679</v>
       </c>
       <c r="V24" t="n">
         <v>-1.842</v>
